--- a/output/pdf_financials_xlsx/GRAY.xlsx
+++ b/output/pdf_financials_xlsx/GRAY.xlsx
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.744987</v>
+        <v>-0.744987</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.225745</v>
+        <v>-0.225745</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.744987</v>
+        <v>-0.744987</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.225745</v>
+        <v>-0.225745</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.744987</v>
+        <v>-0.744987</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.225745</v>
+        <v>-0.225745</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.206224</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-18.624675</v>
+        <v>18.624675</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.744987</v>
+        <v>-0.744987</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.225745</v>
+        <v>-0.225745</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.744987</v>
+        <v>-0.744987</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.225745</v>
+        <v>-0.225745</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.744987</v>
+        <v>-0.744987</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.225745</v>
+        <v>-0.225745</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GRAY.xlsx
+++ b/output/pdf_financials_xlsx/GRAY.xlsx
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.038035</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.009287999999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002976</v>
       </c>
     </row>
     <row r="35">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.038035</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.009287999999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002976</v>
       </c>
     </row>
     <row r="37">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.046852</v>
+        <v>0.008817</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.013831</v>
+        <v>0.004543</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.007237</v>
+        <v>0.004261</v>
       </c>
     </row>
     <row r="49">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
